--- a/Data/QF_Facility_Data_Dictionary.xlsx
+++ b/Data/QF_Facility_Data_Dictionary.xlsx
@@ -1,22 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Start Here" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Codes and Joins" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Orders" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Order Lines" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="SKU Master" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Supplier Fill" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Replenishment" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Modules" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Design Parameters" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Stress Scenarios" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start Here" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Codes and Joins" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Orders" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Order Lines" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SKU Master" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplier Sequence" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Replenishment" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modules" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Design Parameters" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stress Scenarios" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Part 1 uploads" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Platform exports" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changes 2026-10-12" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -26,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,11 +43,13 @@
       <sz val="19"/>
     </font>
     <font>
-      <i val="1"/>
       <color rgb="0044546A"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +59,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00003057"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8EDF3"/>
       </patternFill>
     </fill>
   </fills>
@@ -67,24 +77,31 @@
     </border>
     <border>
       <bottom style="thin">
-        <color rgb="00CCD6E0"/>
+        <color rgb="00D0D5DD"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -159,146 +176,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="FileIndex" displayName="FileIndex" ref="A4:E12" headerRowCount="1">
-  <autoFilter ref="A4:E12"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="File"/>
-    <tableColumn id="2" name="Purpose"/>
-    <tableColumn id="3" name="Released"/>
-    <tableColumn id="4" name="Primary key"/>
-    <tableColumn id="5" name="Connects through"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table10.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="10" name="SchemaStressScenarios" displayName="SchemaStressScenarios" ref="A4:E11" headerRowCount="1">
-  <autoFilter ref="A4:E11"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Field"/>
-    <tableColumn id="2" name="Data type"/>
-    <tableColumn id="3" name="Unit"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Example"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="CodesAndJoins" displayName="CodesAndJoins" ref="A4:E12" headerRowCount="1">
-  <autoFilter ref="A4:E12"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Topic"/>
-    <tableColumn id="2" name="Value"/>
-    <tableColumn id="3" name="Meaning"/>
-    <tableColumn id="4" name="Related file"/>
-    <tableColumn id="5" name="Join field"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="SchemaOrders" displayName="SchemaOrders" ref="A4:E19" headerRowCount="1">
-  <autoFilter ref="A4:E19"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Field"/>
-    <tableColumn id="2" name="Data type"/>
-    <tableColumn id="3" name="Unit"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Example"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="SchemaOrderLines" displayName="SchemaOrderLines" ref="A4:E9" headerRowCount="1">
-  <autoFilter ref="A4:E9"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Field"/>
-    <tableColumn id="2" name="Data type"/>
-    <tableColumn id="3" name="Unit"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Example"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="SchemaSKUMaster" displayName="SchemaSKUMaster" ref="A4:E20" headerRowCount="1">
-  <autoFilter ref="A4:E20"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Field"/>
-    <tableColumn id="2" name="Data type"/>
-    <tableColumn id="3" name="Unit"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Example"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="6" name="SchemaSupplierFill" displayName="SchemaSupplierFill" ref="A4:E10" headerRowCount="1">
-  <autoFilter ref="A4:E10"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Field"/>
-    <tableColumn id="2" name="Data type"/>
-    <tableColumn id="3" name="Unit"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Example"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="SchemaReplenishment" displayName="SchemaReplenishment" ref="A4:E13" headerRowCount="1">
-  <autoFilter ref="A4:E13"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Field"/>
-    <tableColumn id="2" name="Data type"/>
-    <tableColumn id="3" name="Unit"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Example"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table8.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="8" name="SchemaModules" displayName="SchemaModules" ref="A4:E20" headerRowCount="1">
-  <autoFilter ref="A4:E20"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Field"/>
-    <tableColumn id="2" name="Data type"/>
-    <tableColumn id="3" name="Unit"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Example"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
-</file>
-
-<file path=xl/tables/table9.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="9" name="SchemaDesignParameters" displayName="SchemaDesignParameters" ref="A4:E11" headerRowCount="1">
-  <autoFilter ref="A4:E11"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Field"/>
-    <tableColumn id="2" name="Data type"/>
-    <tableColumn id="3" name="Unit"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Example"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -590,7 +467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -614,273 +491,318 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Student-facing guide to files, fields, codes, and joins</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+          <t>Student-facing guide to files, fields, codes, and joins. Package version 2026-10-12.</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>File</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Purpose</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Released</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Primary key</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Connects through</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>QF_Facility_Orders.csv</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Historical order headers</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>At start</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>QF_Facility_Order_Lines.csv</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Products and quantities in each order</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>At start</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>order_id + line_no</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>order_id, sku_id</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>QF_Facility_SKU_Master.csv</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Physical and handling attributes by product</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>At start</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>QF_Facility_Supplier_Fill.csv</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Assigned supplier and fill probabilities</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>QF_Facility_Supplier_Sequence.csv</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Each product's ordered DC sequence under the common full-or-partial supply rule</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>At start</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>QF_Facility_Replenishment_Scenarios.csv</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Supplier delivery calendars</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>DC delivery calendars and booking deadlines by scenario</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>At start</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>scenario_id + supplier</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>scenario_id, supplier</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>QF_Facility_Storage_Modules.csv</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Reference storage, staging, and process modules</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>At start</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>module_id</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>module_id, zone</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>QF_Facility_Design_Parameters.csv</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Given operating and economic parameters</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>At start</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>parameter_group + parameter + option_label</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>parameter</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>QF_Facility_Stress_Scenarios.csv</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Common evaluation scenario settings</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>At start</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>scenario_id</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>scenario_id</t>
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="4" t="n"/>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="n"/>
+      <c r="E13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Sheet 'Part 1 uploads'</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Exact formats of the Task 1 and Task 2 files</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Sheet 'Platform exports'</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Files the QF Design Platform exports</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n"/>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Sheet 'Changes 2026-10-12'</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>What changed since the 2026-09-17 release</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n"/>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" s="4" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -917,235 +839,796 @@
           <t>Common evaluation scenario settings</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Data type</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>scenario_id</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Scenario identifier.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>BASE</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>order_volume_multiplier</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Multiplier applied to order volume.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>affected_sku_share</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Share of products affected by a popularity change.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>affected_sku_demand_multiplier</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Demand multiplier for affected products.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>affected_sku_seed</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Seed selecting affected products consistently.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>20260917</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>picker_availability</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Available share of planned picker capacity.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>inbound_delay_minutes</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>minutes</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Delay applied to scheduled receipts.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="100" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Part 1 uploads</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>The two file formats the QF Design Platform accepts on Register</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Upload</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Task 1 demand estimate</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>demand_estimates.csv</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>sku_id,date,mean_units,sd_units  (optionally ,hour)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Task 1 demand estimate</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>demand_estimates.csv</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Example row</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>P0001,2027-09-07,5.200,2.100</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Task 1 demand estimate</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>demand_estimates.csv</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>One row per product per ISO date. Every product needs a row for every date of the evaluation window (the first 16 weeks of the withheld year, 2027-09-07 to 2027-12-27); dates must lie in the evaluation year (2027-09-07 to 2028-09-05). mean_units and sd_units are numbers from 0; hour, when present, is a whole hour 0-23.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Task 2 ordering alternative</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>one CSV per alternative</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Header</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>policy_id,scenario_id,service_target,sku_id,effective_day,target_stock_units  (optionally followed by any of expected_inventory_units, expected_inventory_service, expected_lost_units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Task 2 ordering alternative</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>one CSV per alternative</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Example row</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>A1,FAST,0.90,P0001,2027-09-07,48</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Task 2 ordering alternative</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>one CSV per alternative</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Rules</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>policy_id is the alternative's id; scenario_id FAST, MEDIUM or SLOW; service_target a number (0.50, 0.90, 0.99; 'mean' is read as 0.50); effective_day an ISO date from which the target applies; target_stock_units a whole number of units from 0; one target per product, scenario and effective_day. expected_inventory_service is a share from 0 to 1; the other expected columns are numbers from 0.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="32" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="100" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Platform exports</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="2" t="n"/>
+      <c r="D1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Files the QF Design Platform exports</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Screen</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Format</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Content</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>&lt;facility_id&gt;_layout.json</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Facility</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>The placed floor (free-floor document, contract v2) plus base_area {w_ft, d_ft}, zones [{name, function, x, y, w, d, temperature}], facility_id, alternative_id and routing. Re-importable on the Facility screen.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>&lt;facility_id&gt;_resources.csv</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Facility</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>module_id,zone,count,positions,capex_usd,energy_kwh_day: one row per module type, counted from the placed floor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>&lt;facility_id&gt;_operating.json</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Facility</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>JSON</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>pickers, promise_min, staging_positions, pickers_by_promise, staging_by_zone (the team's Task 4(c)/(d) estimates), night_crew, policy {basis, sharing, placement}, scenario_id, service_target, routing (fixed: directed shortest feasible).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>QF_Register_&lt;team&gt;.csv</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>CSV</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>The experiment register: one row per run with run_id, alternative, facility, settings, seed, window, routing, part1_hash, ordering file hash, created_at, then the measures. Every row reproduces its run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>QF_Submission_&lt;team&gt;.zip</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Review</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>ZIP</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>files/ (the recorded Part 1 uploads and any product-to-slot file), facilities/&lt;facility_id&gt;/layout.json, resources.csv and operating.json, register.csv and recommendation.json.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="150" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Changes 2026-10-12</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Every change since the 2026-09-17 release</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Order volume. The 2026-09-17 release carried 381,048 orders over the year (1,044 a day on average, up to 1,727 on the busiest day). This release is thinned day by day to 34.7% of those orders: 132,389 over the same 365 days, from 244 to 600 a day (mean 363). The weekday pattern, the time-of-day shape, the baskets, the products and the customer points are unchanged. Opening inventories in QF_Facility_SKU_Master.csv are scaled with the volume. Anything estimated from the orders file has to be redone on this release.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>Order times. In the 2026-09-17 release, 319,906 orders (from 2 November 2026 onward) were stamped 23:59:58 instead of a time. Every order now carries a real time of day, drawn from the valid orders of the same weekday. No order is placed in the 23:00 hour.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>placement_minute now means the same thing on every row: minutes from 00:00 on day 0 (2026-09-07), that is day x 1440 + the minute of the day of placement_timestamp, rising to 525,240 at the end of the year. In the 2026-09-17 release it was cumulative until 2 November 2026 and then only the minute of the day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>order_id now follows placement time: ids rise with day and placement_minute (orders placed in the same second keep a fixed order). Ids are not those of the 2026-09-17 release.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>New column placement_date in QF_Facility_Orders.csv, right after day: the order's calendar date. day stays the 0-based day index (day 0 = 2026-09-07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>QF_Facility_Supplier_Fill.csv is renamed QF_Facility_Supplier_Sequence.csv and its columns change: sku_id, preferred_dc, second_dc, third_dc replace assigned_supplier and the four per-product fill probabilities. The fill rule is now common to all DCs and sits in QF_Facility_Design_Parameters.csv as two supply rows: full_fill_probability (0.95: the DC supplies the whole order) and partial_fill_fraction (0.90: otherwise this share ships and the rest goes to the next DC in the sequence on its next delivery day).</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Column supplier_lead_time_hours is removed from QF_Facility_SKU_Master.csv. Delivery timing comes from the scenarios file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t>QF_Facility_Replenishment_Scenarios.csv has new columns: served_by_dc, cycle_anchor_date, book_day_offset, book_time and available_from. receipt_time is replaced by available_from (06:00, on the shelves on the delivery day). Weekly and longer cycles name their weekday (Every Monday, Every other Monday from 2026-09-07).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>SLOW has no Local DC: products assigned to Local are supplied by the Regional DC, on the Regional calendar and booking deadline (served_by_dc = Regional). The 2026-09-17 row that read "Local, Weekly" under SLOW was wrong.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Booking: an order for delivery day d is booked book_day_offset days before d at book_time. At 18:00 the day's trading is over, so the position is that day's closing stock; at 08:00 it is the previous day's closing stock plus the receipts on the shelves at 06:00 that morning.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>The monthly National delivery in SLOW is now Every four weeks: a 28-day cycle from 2026-09-07, so every delivery falls on a Monday. Monthly is no longer used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>The casework document is no longer in this ZIP (the copy in the 2026-09-17 release was an older text that did not match the PDF); the professor distributes it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>The data dictionary QF_Facility_Data_Dictionary.xlsx is rebuilt: one sheet per file, plus the Part 1 upload formats, the platform's exports, the fixed building elements and this list. The ZIP carries no README or other text file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>Orders placed before 10:00 or after 18:00 (22 in the 2026-09-17 release) now carry a time inside the 10:00-18:00 order day (operating_calendar in QF_Facility_Design_Parameters.csv), drawn from the same weekday time-of-day shape as the other orders.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
@@ -1155,14 +1638,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E12"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
     <col width="52" customWidth="1" min="3" max="3"/>
     <col width="38" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -1182,262 +1665,374 @@
           <t>Given encodings and file connections only</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Topic</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Meaning</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Related file</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Join field</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>day_of_week</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>0–6</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>0-6</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>Monday through Sunday</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Orders</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="4" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>day</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>0-364</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Day index; day 0 is 2026-09-07 (placement_date gives the date)</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Orders</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>temperature_zone</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Ambient / Chilled / Frozen</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>Product handling zone</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Order Lines, SKU Master</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>supplier</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Local / Regional / National</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Assigned inbound source</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Supplier Fill, Replenishment</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>supplier</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>DC a product is assigned to (its preferred_dc)</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Supplier Sequence, Replenishment</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>preferred_dc = supplier</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>served_by_dc</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Local / Regional / National</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>DC that ships; Regional for Local products in SLOW</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Replenishment</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>replenishment scenario</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>FAST / MEDIUM / SLOW</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>Calendar alternative</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Replenishment</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>scenario_id</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>frequency_label</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Daily / Twice weekly / Weekly / Every two weeks / Every four weeks</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Delivery frequency; every four weeks is a 28-day cycle</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Replenishment</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>twice weekly</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Sunday and Thursday</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>Four-day then three-day gaps</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Replenishment</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="E12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>booking</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>book_day_offset, book_time</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Order for delivery day d is booked book_day_offset days before d at book_time</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Replenishment</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>orders to lines</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>One order to many product lines</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Orders, Order Lines</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>products to lines</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>One product to many order lines</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>SKU Master, Order Lines</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>products to supply</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>One product to one baseline supplier row</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>SKU Master, Supplier Fill</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>One product to one DC-sequence row</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>SKU Master, Supplier Sequence</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>products to calendar</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>preferred_dc</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>A product's calendar is its scenario row with supplier = preferred_dc</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Supplier Sequence, Replenishment</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>scenario_id + supplier</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -1447,7 +2042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1474,427 +2069,455 @@
           <t>Historical order headers</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Data type</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Key joining an order header to its order lines.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Key joining an order header to its order lines. Ids rise with placement time.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>order_reference</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Display identifier for an order.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>QF-01-000551</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>day</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Zero-based day in the historical file.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>day index</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>Zero-based day index of the history: day 0 is 2026-09-07.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>placement_date</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>ISO date</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>Calendar date of the order: 2026-09-07 + day.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>day_of_week</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Zero-based weekday where 0 is Monday.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>weekend</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Whether the date is Saturday or Sunday.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>placement_minute</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>minute of day</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Minutes after midnight when the order was placed.</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>minutes from day 0</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Minutes from 00:00 on 2026-09-07: day x 1440 + the minute of the day of placement_timestamp.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>600.667</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>placement_timestamp</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Order-placement timestamp.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>ISO date-time</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Order-placement date and time, to the second.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>2026-09-07T10:00:40</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>facility_id</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Quick Fulfiller identifier.</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>QF_CENTRAL</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>customer_point_id</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="4" t="n"/>
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Synthetic customer demand-point identifier.</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>DP_0904</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>customer_latitude</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>degrees</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Synthetic customer latitude.</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>33.727413</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>customer_longitude</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>degrees</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Synthetic customer longitude.</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>-84.363606</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>customer_distance_miles</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>miles</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Planning distance from the QF.</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>4.428</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>basket_size_units</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>units</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Total units requested by the order.</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Total units requested by the order; equals the sum of its lines' quantity.</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>estimated_delivery_minutes</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>minutes</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Estimated travel time from handoff to the customer.</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>13.7</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>courier_arrival_offset_minutes</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>minutes</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Signed difference between latest staged-ready time and courier arrival. Negative values indicate early arrival.</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -1931,173 +2554,166 @@
           <t>Products and quantities in each order</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Data type</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>order_id</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Key joining an order header to its order lines.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>line_no</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Line sequence within an order.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Product identifier.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>P0002</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>quantity</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>units</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Requested units on the order line.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>temperature_zone</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Required temperature zone.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Ambient</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -2107,7 +2723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2134,466 +2750,432 @@
           <t>Physical and handling attributes by product</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Data type</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Product identifier.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>P0001</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>temperature_zone</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Required temperature zone.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Ambient</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>product_family_id</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Synthetic product-family identifier.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>F01</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>unit_width_cm</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>cm</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Product envelope width.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>8.6</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>unit_depth_cm</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>cm</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Product envelope depth.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>unit_height_cm</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>cm</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Product envelope height.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>unit_volume_l</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>litres</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Product envelope volume.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>0.503</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>unit_weight_kg</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Product unit weight.</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>0.156</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>case_pack_units</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C13" s="4" t="inlineStr">
         <is>
           <t>units/case</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Units in one inbound case.</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>opening_on_hand_units</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>units</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Units available at the beginning of the history.</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1344</t>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>480</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>minimum_inbound_order_casepacks</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>case packs</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Smallest allowed inbound order in case packs.</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Smallest inbound order in case packs. It is a floor on an order, never a reason to skip one.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>case_volume_l</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>litres</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Volume of one inbound case.</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>14.17</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>shelf_life_days</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Product shelf life.</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>103</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>fragile</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr"/>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Whether the product requires fragile handling.</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>stackability</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr"/>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C19" s="4" t="n"/>
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Given stackability category.</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>supplier_lead_time_hours</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>hours</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Given supplier lead time.</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -2603,7 +3185,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2616,7 +3198,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>QF_Facility_Supplier_Fill.csv</t>
+          <t>QF_Facility_Supplier_Sequence.csv</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2627,211 +3209,142 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Assigned supplier and fill probabilities</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+          <t>Each product's ordered DC sequence under the common full-or-partial supply rule</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Data type</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>sku_id</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Product identifier.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>P0001</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>assigned_supplier</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>preferred_dc</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Supplier assigned to the product for the baseline case.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>DC to which the complete order quantity is first presented: Local, Regional or National.</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>second_dc</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>DC presented with what the preferred DC leaves unfilled; blank when the sequence stops before.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>assigned_fill_probability</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>fraction</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Full-fill probability for the assigned supplier.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0.912</t>
-        </is>
-      </c>
-    </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>local_fill_probability</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>fraction</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Local supplier full-fill probability.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0.967</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>regional_fill_probability</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>fraction</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Regional supplier full-fill probability.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0.912</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>national_fill_probability</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Decimal</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>fraction</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>National supplier full-fill probability.</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0.853</t>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>third_dc</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>DC presented with what the second DC leaves unfilled; blank when the sequence stops before.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>National</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -2841,7 +3354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2865,268 +3378,369 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Supplier delivery calendars</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+          <t>DC delivery calendars and booking deadlines by scenario</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Data type</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>scenario_id</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Scenario identifier.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Scenario identifier: FAST, MEDIUM or SLOW.</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>FAST</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>scenario_name</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Scenario display name.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Fast Replenishment</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>supplier</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Supplier name.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>The DC the product is assigned to (its preferred_dc): Local, Regional or National.</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Local</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>served_by_dc</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>The DC that ships, whose calendar and booking deadline apply. Differs from supplier only in SLOW, which has no Local DC: Local products are supplied by the Regional DC.</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>Local</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>frequency_label</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Delivery-frequency label.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Daily, Twice weekly, Weekly, Every two weeks or Every four weeks.</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>Daily</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>nominal_interval_days</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>days</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Average interval supplied for analytical use.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Average interval between deliveries, for analytical use (3.5 for twice weekly).</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>scheduled_days</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Calendar rule for deliveries.</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Calendar rule for deliveries, in words.</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Every day</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>interval_pattern_days</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Sequence of calendar gaps between deliveries.</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Gaps between deliveries; '4 then 3' for Sunday and Thursday.</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>receipt_time</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>cycle_anchor_date</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>ISO date</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>First delivery of a fixed cycle: deliveries fall every interval_pattern_days days from this date, in both years. Blank for daily and named-weekday calendars.</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>book_day_offset</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>days</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Days before the delivery day on which the order is booked.</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>book_time</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>time</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Scheduled receipt time.</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Booking time on that day. 18:00 is after the day's trading: the position is that day's closing stock. 08:00 is before trading: the position is the previous day's closing stock plus the receipts on the shelves at 06:00 that morning.</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>available_from</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Time on the delivery day the goods are on the shelves (received overnight).</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>06:00</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>planning_note</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Clarification attached to the calendar rule.</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>Book by 18:00 on day d-1; the goods are received overnight and are on the shelves at 06:00 on day d.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -3136,7 +3750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:N39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3144,6 +3758,15 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="72" customWidth="1" min="4" max="4"/>
     <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -3163,462 +3786,1013 @@
           <t>Reference storage, staging, and process modules</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Data type</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>module_id</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Module identifier.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>AMB-SHELF</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>module_category</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Storage, Staging, Consolidation, or Order Control.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>Storage</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>zone</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Applicable temperature or process zone.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>Ambient</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>width_ft</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="inlineStr">
         <is>
           <t>feet</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Exterior width.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>4.0</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>depth_ft</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>feet</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Exterior depth.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>height_ft</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C10" s="4" t="inlineStr">
         <is>
           <t>feet</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Exterior height.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>usable_levels</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Levels available for positions.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>positions_per_level</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr"/>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="inlineStr">
         <is>
           <t>Addressed positions across one level.</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>total_positions</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="4" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr"/>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C13" s="4" t="n"/>
+      <c r="D13" s="4" t="inlineStr">
         <is>
           <t>Total addressed positions in the module.</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="4" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>position_width_ft</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
+      <c r="C14" s="4" t="inlineStr">
         <is>
           <t>feet</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="4" t="inlineStr">
         <is>
           <t>Position width.</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E14" s="4" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>position_depth_ft</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C15" s="4" t="inlineStr">
         <is>
           <t>feet</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
         <is>
           <t>Position depth.</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="4" t="inlineStr">
         <is>
           <t>2.0</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>position_height_ft</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C16" s="4" t="inlineStr">
         <is>
           <t>feet</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="4" t="inlineStr">
         <is>
           <t>Position height.</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="4" t="inlineStr">
         <is>
           <t>1.4</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>usable_cube_factor</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C17" s="4" t="inlineStr">
         <is>
           <t>fraction</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="4" t="inlineStr">
         <is>
           <t>Share of nominal cube available for product storage.</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="4" t="inlineStr">
         <is>
           <t>0.82</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>usable_position_volume_l</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C18" s="4" t="inlineStr">
         <is>
           <t>litres</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="4" t="inlineStr">
         <is>
           <t>Usable volume of one product position.</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>capex_usd</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>Installed capital cost.</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>420</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>energy_kwh_day</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="4" t="inlineStr">
         <is>
           <t>Decimal</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
+      <c r="C20" s="4" t="inlineStr">
         <is>
           <t>kWh/day</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="4" t="inlineStr">
         <is>
           <t>Daily energy use.</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E20" s="4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
     </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Reference modules (the QF Design Platform renders exactly these rows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>module_id</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>Display name</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>Width ft</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>Depth ft</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>Height ft</t>
+        </is>
+      </c>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t>Levels</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Positions / level</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Total positions</t>
+        </is>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>Usable L / position</t>
+        </is>
+      </c>
+      <c r="L23" s="6" t="inlineStr">
+        <is>
+          <t>Cube factor</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>Capex USD</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="inlineStr">
+        <is>
+          <t>Energy kWh/day</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AMB-SHELF</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Ambient shelving bay</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>7</v>
+      </c>
+      <c r="H24" t="n">
+        <v>5</v>
+      </c>
+      <c r="I24" t="n">
+        <v>4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>20</v>
+      </c>
+      <c r="K24" t="n">
+        <v>65</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M24" t="n">
+        <v>420</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>CHL-CAB</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Chilled cabinet</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Chilled</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>4</v>
+      </c>
+      <c r="F25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>7</v>
+      </c>
+      <c r="H25" t="n">
+        <v>5</v>
+      </c>
+      <c r="I25" t="n">
+        <v>4</v>
+      </c>
+      <c r="J25" t="n">
+        <v>20</v>
+      </c>
+      <c r="K25" t="n">
+        <v>73.3</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="M25" t="n">
+        <v>7600</v>
+      </c>
+      <c r="N25" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>FRZ-CAB</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Frozen cabinet</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Storage</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Frozen</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>4</v>
+      </c>
+      <c r="F26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G26" t="n">
+        <v>7</v>
+      </c>
+      <c r="H26" t="n">
+        <v>5</v>
+      </c>
+      <c r="I26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J26" t="n">
+        <v>20</v>
+      </c>
+      <c r="K26" t="n">
+        <v>83.3</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M26" t="n">
+        <v>9800</v>
+      </c>
+      <c r="N26" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PACK-BENCH</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Consolidation bench</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Consolidation</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>8</v>
+      </c>
+      <c r="F27" t="n">
+        <v>3</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1900</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ORDER-CONTROL</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Order control</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Order Control</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>All</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>5</v>
+      </c>
+      <c r="F28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>4</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>2800</v>
+      </c>
+      <c r="N28" t="n">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>STAGE-AMB-RACK</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Ambient staging rack</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Staging</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Ambient</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" t="n">
+        <v>2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>7</v>
+      </c>
+      <c r="H29" t="n">
+        <v>4</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>12</v>
+      </c>
+      <c r="M29" t="n">
+        <v>650</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>STAGE-CHL-CAB</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Chilled staging cabinet</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Staging</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Chilled</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>4</v>
+      </c>
+      <c r="F30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G30" t="n">
+        <v>7</v>
+      </c>
+      <c r="H30" t="n">
+        <v>4</v>
+      </c>
+      <c r="I30" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" t="n">
+        <v>12</v>
+      </c>
+      <c r="M30" t="n">
+        <v>8200</v>
+      </c>
+      <c r="N30" t="n">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>STAGE-FRZ-CAB</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Frozen staging cabinet</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Staging</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Frozen</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" t="n">
+        <v>3</v>
+      </c>
+      <c r="G31" t="n">
+        <v>7</v>
+      </c>
+      <c r="H31" t="n">
+        <v>4</v>
+      </c>
+      <c r="I31" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" t="n">
+        <v>12</v>
+      </c>
+      <c r="M31" t="n">
+        <v>10400</v>
+      </c>
+      <c r="N31" t="n">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Positions are addressed slots (storage) or staged-order places (staging). Usable volume already includes the cube factor; do not apply it twice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Fixed building elements (not modules; sizes set by the QF Design Platform)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Element</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>Width ft</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Depth ft</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>Placement</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Dock door</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>24</v>
+      </c>
+      <c r="C37" t="n">
+        <v>12</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>On an outside wall; receiving apron included</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Handoff door</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>4</v>
+      </c>
+      <c r="C38" t="n">
+        <v>12</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>On an outside wall; couriers collect here</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Basket and cart station</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>6</v>
+      </c>
+      <c r="C39" t="n">
+        <v>4</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Anywhere on the floor; every picking tour starts and ends here</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -3655,206 +4829,199 @@
           <t>Given operating and economic parameters</t>
         </is>
       </c>
-      <c r="B2" s="2" t="n"/>
-      <c r="C2" s="2" t="n"/>
-      <c r="D2" s="2" t="n"/>
-      <c r="E2" s="2" t="n"/>
+      <c r="B2" s="4" t="n"/>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="n"/>
-      <c r="B3" s="2" t="n"/>
-      <c r="C3" s="2" t="n"/>
-      <c r="D3" s="2" t="n"/>
-      <c r="E3" s="2" t="n"/>
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+      <c r="D3" s="4" t="n"/>
+      <c r="E3" s="4" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Field</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Data type</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Example</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>parameter_group</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr"/>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>Parameter category.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
         <is>
           <t>metadata</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>parameter</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>Machine-readable parameter name.</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="4" t="inlineStr">
         <is>
           <t>data_type</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>option_label</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr"/>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="4" t="n"/>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>Label distinguishing parameter alternatives.</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="E7" s="4" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>value</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="inlineStr">
         <is>
           <t>Parameter value.</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>synthetic engineering test data</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>unit</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>Measurement unit.</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr"/>
+      <c r="E9" s="4" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>data_type</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr"/>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="4" t="n"/>
+      <c r="D10" s="4" t="inlineStr">
         <is>
           <t>Expected value type.</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="4" t="inlineStr">
         <is>
           <t>text</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Text</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="4" t="n"/>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>Parameter description.</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>Data type.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>